--- a/data/nzd0352/nzd0352.xlsx
+++ b/data/nzd0352/nzd0352.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H447"/>
+  <dimension ref="A1:H449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13848,6 +13848,66 @@
       <c r="H447" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:07:32+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>289.36</v>
+      </c>
+      <c r="C448" t="n">
+        <v>344.38</v>
+      </c>
+      <c r="D448" t="n">
+        <v>339.23</v>
+      </c>
+      <c r="E448" t="n">
+        <v>328.26</v>
+      </c>
+      <c r="F448" t="n">
+        <v>323.13</v>
+      </c>
+      <c r="G448" t="n">
+        <v>431.92</v>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="C449" t="n">
+        <v>344.88</v>
+      </c>
+      <c r="D449" t="n">
+        <v>340.24</v>
+      </c>
+      <c r="E449" t="n">
+        <v>329.98</v>
+      </c>
+      <c r="F449" t="n">
+        <v>324.6</v>
+      </c>
+      <c r="G449" t="n">
+        <v>431.98</v>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13862,7 +13922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B458"/>
+  <dimension ref="A1:B460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18445,6 +18505,26 @@
       </c>
       <c r="B458" t="n">
         <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>-0.18</v>
       </c>
     </row>
   </sheetData>
@@ -18613,28 +18693,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.200856321188736</v>
+        <v>1.197643624873377</v>
       </c>
       <c r="J2" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K2" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03843763728815219</v>
+        <v>0.03859145720899004</v>
       </c>
       <c r="M2" t="n">
-        <v>38.34839188642349</v>
+        <v>38.1963740249122</v>
       </c>
       <c r="N2" t="n">
-        <v>2005.757565575371</v>
+        <v>1996.916934633121</v>
       </c>
       <c r="O2" t="n">
-        <v>44.78568482869689</v>
+        <v>44.68687653700045</v>
       </c>
       <c r="P2" t="n">
-        <v>265.6748330288303</v>
+        <v>265.7074703634344</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18691,28 +18771,28 @@
         <v>0.1532</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09049403267337242</v>
+        <v>0.09198006132187561</v>
       </c>
       <c r="J3" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K3" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002871914432711953</v>
+        <v>0.002994859134754502</v>
       </c>
       <c r="M3" t="n">
-        <v>7.725170801354104</v>
+        <v>7.696097022210905</v>
       </c>
       <c r="N3" t="n">
-        <v>159.211089093763</v>
+        <v>158.5135543790961</v>
       </c>
       <c r="O3" t="n">
-        <v>12.61788766370041</v>
+        <v>12.59021661366857</v>
       </c>
       <c r="P3" t="n">
-        <v>340.5467607185763</v>
+        <v>340.5317356316728</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18769,28 +18849,28 @@
         <v>0.0784</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03014382197590783</v>
+        <v>-0.03269758545171803</v>
       </c>
       <c r="J4" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K4" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002483578198440917</v>
+        <v>0.002943198466102248</v>
       </c>
       <c r="M4" t="n">
-        <v>3.652011309304061</v>
+        <v>3.648964389767255</v>
       </c>
       <c r="N4" t="n">
-        <v>20.43585554077723</v>
+        <v>20.38401526104841</v>
       </c>
       <c r="O4" t="n">
-        <v>4.520603448741908</v>
+        <v>4.514866029136237</v>
       </c>
       <c r="P4" t="n">
-        <v>343.4721697705522</v>
+        <v>343.4979864443382</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18847,28 +18927,28 @@
         <v>0.0551</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2920805317475514</v>
+        <v>0.2838975434997016</v>
       </c>
       <c r="J5" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K5" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0950886522478479</v>
+        <v>0.09037830056667673</v>
       </c>
       <c r="M5" t="n">
-        <v>5.541163554452933</v>
+        <v>5.561325994924482</v>
       </c>
       <c r="N5" t="n">
-        <v>45.46074409813572</v>
+        <v>45.65390467417221</v>
       </c>
       <c r="O5" t="n">
-        <v>6.742458312673184</v>
+        <v>6.756767324258858</v>
       </c>
       <c r="P5" t="n">
-        <v>330.9155612530276</v>
+        <v>330.9982886235942</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18925,28 +19005,28 @@
         <v>0.092</v>
       </c>
       <c r="I6" t="n">
-        <v>0.100668536227162</v>
+        <v>0.09488510242669669</v>
       </c>
       <c r="J6" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K6" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01145791745047753</v>
+        <v>0.01024769811269843</v>
       </c>
       <c r="M6" t="n">
-        <v>5.803601761200137</v>
+        <v>5.80898756654958</v>
       </c>
       <c r="N6" t="n">
-        <v>48.95882169076582</v>
+        <v>48.93890816256328</v>
       </c>
       <c r="O6" t="n">
-        <v>6.997058073988368</v>
+        <v>6.995634936341609</v>
       </c>
       <c r="P6" t="n">
-        <v>327.9028985429063</v>
+        <v>327.9613666071854</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19003,28 +19083,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03810204555156958</v>
+        <v>-0.03729634367448265</v>
       </c>
       <c r="J7" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K7" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01852997134876122</v>
+        <v>0.01792015140405134</v>
       </c>
       <c r="M7" t="n">
-        <v>1.602254871344974</v>
+        <v>1.599201385546735</v>
       </c>
       <c r="N7" t="n">
-        <v>4.305790093861083</v>
+        <v>4.29037900113149</v>
       </c>
       <c r="O7" t="n">
-        <v>2.075039781271936</v>
+        <v>2.071323007435463</v>
       </c>
       <c r="P7" t="n">
-        <v>432.0161870314943</v>
+        <v>432.0080411388604</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19062,7 +19142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H447"/>
+  <dimension ref="A1:H449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37835,6 +37915,90 @@
         </is>
       </c>
     </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:07:32+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>-41.386250766386254,174.05993039724262</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>-41.386548134493715,174.05888512735302</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>-41.38651447622832,174.05798062844093</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>-41.3866217844106,174.05704302092067</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>-41.38695125714325,174.05614948237795</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>-41.38808045412958,174.056675205838</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>-41.38632157921874,174.0599051813523</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>-41.38655260604399,174.05888441763855</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>-41.386523449110136,174.0579826156344</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>-41.38663597947556,174.0570512588892</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>-41.386961002525766,174.056161382867</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>-41.38808075967951,174.05667579770625</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0352/nzd0352.xlsx
+++ b/data/nzd0352/nzd0352.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H449"/>
+  <dimension ref="A1:H450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13908,6 +13908,36 @@
       <c r="H449" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:30+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>307.49</v>
+      </c>
+      <c r="C450" t="n">
+        <v>344.91</v>
+      </c>
+      <c r="D450" t="n">
+        <v>340.73</v>
+      </c>
+      <c r="E450" t="n">
+        <v>329.43</v>
+      </c>
+      <c r="F450" t="n">
+        <v>325.83</v>
+      </c>
+      <c r="G450" t="n">
+        <v>432.33</v>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13922,7 +13952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B460"/>
+  <dimension ref="A1:B461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18525,6 +18555,16 @@
       </c>
       <c r="B460" t="n">
         <v>-0.18</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>
@@ -18693,28 +18733,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.197643624873377</v>
+        <v>1.20214886434377</v>
       </c>
       <c r="J2" t="n">
+        <v>449</v>
+      </c>
+      <c r="K2" t="n">
         <v>448</v>
       </c>
-      <c r="K2" t="n">
-        <v>447</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.03859145720899004</v>
+        <v>0.03904446131505368</v>
       </c>
       <c r="M2" t="n">
-        <v>38.1963740249122</v>
+        <v>38.13214209519872</v>
       </c>
       <c r="N2" t="n">
-        <v>1996.916934633121</v>
+        <v>1992.698270633988</v>
       </c>
       <c r="O2" t="n">
-        <v>44.68687653700045</v>
+        <v>44.63964908726308</v>
       </c>
       <c r="P2" t="n">
-        <v>265.7074703634344</v>
+        <v>265.6616070892276</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18771,28 +18811,28 @@
         <v>0.1532</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09198006132187561</v>
+        <v>0.09282914589140713</v>
       </c>
       <c r="J3" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K3" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002994859134754502</v>
+        <v>0.003064511571023942</v>
       </c>
       <c r="M3" t="n">
-        <v>7.696097022210905</v>
+        <v>7.682034139730392</v>
       </c>
       <c r="N3" t="n">
-        <v>158.5135543790961</v>
+        <v>158.1690836190537</v>
       </c>
       <c r="O3" t="n">
-        <v>12.59021661366857</v>
+        <v>12.57652907677844</v>
       </c>
       <c r="P3" t="n">
-        <v>340.5317356316728</v>
+        <v>340.5231381401075</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18849,28 +18889,28 @@
         <v>0.0784</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03269758545171803</v>
+        <v>-0.03352391801065566</v>
       </c>
       <c r="J4" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K4" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002943198466102248</v>
+        <v>0.003106781164412764</v>
       </c>
       <c r="M4" t="n">
-        <v>3.648964389767255</v>
+        <v>3.645108629020624</v>
       </c>
       <c r="N4" t="n">
-        <v>20.38401526104841</v>
+        <v>20.34672974968122</v>
       </c>
       <c r="O4" t="n">
-        <v>4.514866029136237</v>
+        <v>4.51073494562485</v>
       </c>
       <c r="P4" t="n">
-        <v>343.4979864443382</v>
+        <v>343.5063535581223</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18927,28 +18967,28 @@
         <v>0.0551</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2838975434997016</v>
+        <v>0.280008456684914</v>
       </c>
       <c r="J5" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K5" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09037830056667673</v>
+        <v>0.08820014727955672</v>
       </c>
       <c r="M5" t="n">
-        <v>5.561325994924482</v>
+        <v>5.570310128444528</v>
       </c>
       <c r="N5" t="n">
-        <v>45.65390467417221</v>
+        <v>45.73193756517279</v>
       </c>
       <c r="O5" t="n">
-        <v>6.756767324258858</v>
+        <v>6.762539283817344</v>
       </c>
       <c r="P5" t="n">
-        <v>330.9982886235942</v>
+        <v>331.0376679649302</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19005,28 +19045,28 @@
         <v>0.092</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09488510242669669</v>
+        <v>0.09289009773450685</v>
       </c>
       <c r="J6" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K6" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01024769811269843</v>
+        <v>0.009862232140073757</v>
       </c>
       <c r="M6" t="n">
-        <v>5.80898756654958</v>
+        <v>5.806787191171836</v>
       </c>
       <c r="N6" t="n">
-        <v>48.93890816256328</v>
+        <v>48.87720284849946</v>
       </c>
       <c r="O6" t="n">
-        <v>6.995634936341609</v>
+        <v>6.991223272682647</v>
       </c>
       <c r="P6" t="n">
-        <v>327.9613666071854</v>
+        <v>327.9815672286891</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19083,28 +19123,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03729634367448265</v>
+        <v>-0.03673438572238585</v>
       </c>
       <c r="J7" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K7" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01792015140405134</v>
+        <v>0.01745963779650761</v>
       </c>
       <c r="M7" t="n">
-        <v>1.599201385546735</v>
+        <v>1.59848431270626</v>
       </c>
       <c r="N7" t="n">
-        <v>4.29037900113149</v>
+        <v>4.284575820555702</v>
       </c>
       <c r="O7" t="n">
-        <v>2.071323007435463</v>
+        <v>2.069921694305294</v>
       </c>
       <c r="P7" t="n">
-        <v>432.0080411388604</v>
+        <v>432.0023509768594</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19142,7 +19182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H449"/>
+  <dimension ref="A1:H450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37999,6 +38039,48 @@
         </is>
       </c>
     </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:30+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>-41.38640848586893,174.05987423450503</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>-41.38655287433703,174.0588843750557</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>-41.3865278022904,174.05798357971852</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>-41.38663144035603,174.05704862465467</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>-41.386969156824414,174.0561713404218</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>-41.388082542053965,174.0566792502712</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0352/nzd0352.xlsx
+++ b/data/nzd0352/nzd0352.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H450"/>
+  <dimension ref="A1:H451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13936,6 +13936,36 @@
         <v>432.33</v>
       </c>
       <c r="H450" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:29+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>307.49</v>
+      </c>
+      <c r="C451" t="n">
+        <v>344.79</v>
+      </c>
+      <c r="D451" t="n">
+        <v>340.83</v>
+      </c>
+      <c r="E451" t="n">
+        <v>329.33</v>
+      </c>
+      <c r="F451" t="n">
+        <v>326.3</v>
+      </c>
+      <c r="G451" t="n">
+        <v>432.5</v>
+      </c>
+      <c r="H451" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13952,7 +13982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B461"/>
+  <dimension ref="A1:B462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18565,6 +18595,16 @@
       </c>
       <c r="B461" t="n">
         <v>0.78</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>
@@ -18733,28 +18773,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.20214886434377</v>
+        <v>1.206586706355618</v>
       </c>
       <c r="J2" t="n">
+        <v>450</v>
+      </c>
+      <c r="K2" t="n">
         <v>449</v>
       </c>
-      <c r="K2" t="n">
-        <v>448</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.03904446131505368</v>
+        <v>0.0394971555308653</v>
       </c>
       <c r="M2" t="n">
-        <v>38.13214209519872</v>
+        <v>38.06788462990377</v>
       </c>
       <c r="N2" t="n">
-        <v>1992.698270633988</v>
+        <v>1988.492700688954</v>
       </c>
       <c r="O2" t="n">
-        <v>44.63964908726308</v>
+        <v>44.59251843851112</v>
       </c>
       <c r="P2" t="n">
-        <v>265.6616070892276</v>
+        <v>265.6163385460731</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18811,28 +18851,28 @@
         <v>0.1532</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09282914589140713</v>
+        <v>0.09361641689346809</v>
       </c>
       <c r="J3" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K3" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003064511571023942</v>
+        <v>0.003131137819930019</v>
       </c>
       <c r="M3" t="n">
-        <v>7.682034139730392</v>
+        <v>7.667798955556195</v>
       </c>
       <c r="N3" t="n">
-        <v>158.1690836190537</v>
+        <v>157.8249883366373</v>
       </c>
       <c r="O3" t="n">
-        <v>12.57652907677844</v>
+        <v>12.56284157094395</v>
       </c>
       <c r="P3" t="n">
-        <v>340.5231381401075</v>
+        <v>340.5151503250723</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18889,28 +18929,28 @@
         <v>0.0784</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03352391801065566</v>
+        <v>-0.03429720396362614</v>
       </c>
       <c r="J4" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K4" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003106781164412764</v>
+        <v>0.00326551613678705</v>
       </c>
       <c r="M4" t="n">
-        <v>3.645108629020624</v>
+        <v>3.641029877757749</v>
       </c>
       <c r="N4" t="n">
-        <v>20.34672974968122</v>
+        <v>20.30864609014105</v>
       </c>
       <c r="O4" t="n">
-        <v>4.51073494562485</v>
+        <v>4.506511521137059</v>
       </c>
       <c r="P4" t="n">
-        <v>343.5063535581223</v>
+        <v>343.514199477946</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18967,28 +19007,28 @@
         <v>0.0551</v>
       </c>
       <c r="I5" t="n">
-        <v>0.280008456684914</v>
+        <v>0.2761106525411505</v>
       </c>
       <c r="J5" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K5" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08820014727955672</v>
+        <v>0.08603176234359466</v>
       </c>
       <c r="M5" t="n">
-        <v>5.570310128444528</v>
+        <v>5.57924740064828</v>
       </c>
       <c r="N5" t="n">
-        <v>45.73193756517279</v>
+        <v>45.81149852941063</v>
       </c>
       <c r="O5" t="n">
-        <v>6.762539283817344</v>
+        <v>6.768419204615701</v>
       </c>
       <c r="P5" t="n">
-        <v>331.0376679649302</v>
+        <v>331.0772158950107</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19045,28 +19085,28 @@
         <v>0.092</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09289009773450685</v>
+        <v>0.09111854577203507</v>
       </c>
       <c r="J6" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K6" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009862232140073757</v>
+        <v>0.009530533105775785</v>
       </c>
       <c r="M6" t="n">
-        <v>5.806787191171836</v>
+        <v>5.803358016727858</v>
       </c>
       <c r="N6" t="n">
-        <v>48.87720284849946</v>
+        <v>48.80601478684013</v>
       </c>
       <c r="O6" t="n">
-        <v>6.991223272682647</v>
+        <v>6.986130172480336</v>
       </c>
       <c r="P6" t="n">
-        <v>327.9815672286891</v>
+        <v>327.999541762699</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19123,28 +19163,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03673438572238585</v>
+        <v>-0.03610640449639037</v>
       </c>
       <c r="J7" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K7" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01745963779650761</v>
+        <v>0.01693815272135857</v>
       </c>
       <c r="M7" t="n">
-        <v>1.59848431270626</v>
+        <v>1.598091470067461</v>
       </c>
       <c r="N7" t="n">
-        <v>4.284575820555702</v>
+        <v>4.279757611667846</v>
       </c>
       <c r="O7" t="n">
-        <v>2.069921694305294</v>
+        <v>2.068757504316987</v>
       </c>
       <c r="P7" t="n">
-        <v>432.0023509768594</v>
+        <v>431.995979348963</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19182,7 +19222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H450"/>
+  <dimension ref="A1:H451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38081,6 +38121,48 @@
         </is>
       </c>
     </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:29+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>-41.38640848586893,174.05987423450503</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>-41.38655180116495,174.05888454538717</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>-41.38652869069454,174.05798377647042</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>-41.386630615061556,174.057048145703</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>-41.386972272694386,174.0561751453418</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>-41.388083407778666,174.05668092723138</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0352/nzd0352.xlsx
+++ b/data/nzd0352/nzd0352.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H451"/>
+  <dimension ref="A1:H452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13968,6 +13968,36 @@
       <c r="H451" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>322.28</v>
+      </c>
+      <c r="C452" t="n">
+        <v>343.83</v>
+      </c>
+      <c r="D452" t="n">
+        <v>342.54</v>
+      </c>
+      <c r="E452" t="n">
+        <v>332.34</v>
+      </c>
+      <c r="F452" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="G452" t="n">
+        <v>432.63</v>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13982,7 +14012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B462"/>
+  <dimension ref="A1:B463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18605,6 +18635,16 @@
       </c>
       <c r="B462" t="n">
         <v>0.64</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -18773,28 +18813,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.206586706355618</v>
+        <v>1.217391445854439</v>
       </c>
       <c r="J2" t="n">
+        <v>451</v>
+      </c>
+      <c r="K2" t="n">
         <v>450</v>
       </c>
-      <c r="K2" t="n">
-        <v>449</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0394971555308653</v>
+        <v>0.04033958614015942</v>
       </c>
       <c r="M2" t="n">
-        <v>38.06788462990377</v>
+        <v>38.03349923729091</v>
       </c>
       <c r="N2" t="n">
-        <v>1988.492700688954</v>
+        <v>1985.430085278093</v>
       </c>
       <c r="O2" t="n">
-        <v>44.59251843851112</v>
+        <v>44.55816519200598</v>
       </c>
       <c r="P2" t="n">
-        <v>265.6163385460731</v>
+        <v>265.5053538554376</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18851,28 +18891,28 @@
         <v>0.1532</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09361641689346809</v>
+        <v>0.09398327661741454</v>
       </c>
       <c r="J3" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K3" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003131137819930019</v>
+        <v>0.003170817154295791</v>
       </c>
       <c r="M3" t="n">
-        <v>7.667798955556195</v>
+        <v>7.652097695271117</v>
       </c>
       <c r="N3" t="n">
-        <v>157.8249883366373</v>
+        <v>157.4766233134382</v>
       </c>
       <c r="O3" t="n">
-        <v>12.56284157094395</v>
+        <v>12.54896901396438</v>
       </c>
       <c r="P3" t="n">
-        <v>340.5151503250723</v>
+        <v>340.5114019191872</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18929,28 +18969,28 @@
         <v>0.0784</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03429720396362614</v>
+        <v>-0.03432589734878678</v>
       </c>
       <c r="J4" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K4" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00326551613678705</v>
+        <v>0.003286716760777963</v>
       </c>
       <c r="M4" t="n">
-        <v>3.641029877757749</v>
+        <v>3.633104031292895</v>
       </c>
       <c r="N4" t="n">
-        <v>20.30864609014105</v>
+        <v>20.26362549520682</v>
       </c>
       <c r="O4" t="n">
-        <v>4.506511521137059</v>
+        <v>4.501513689327938</v>
       </c>
       <c r="P4" t="n">
-        <v>343.514199477946</v>
+        <v>343.5144926539115</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19007,28 +19047,28 @@
         <v>0.0551</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2761106525411505</v>
+        <v>0.2734985962606997</v>
       </c>
       <c r="J5" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K5" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08603176234359466</v>
+        <v>0.08478662609242138</v>
       </c>
       <c r="M5" t="n">
-        <v>5.57924740064828</v>
+        <v>5.580936785198328</v>
       </c>
       <c r="N5" t="n">
-        <v>45.81149852941063</v>
+        <v>45.78999459588035</v>
       </c>
       <c r="O5" t="n">
-        <v>6.768419204615701</v>
+        <v>6.76683046897736</v>
       </c>
       <c r="P5" t="n">
-        <v>331.0772158950107</v>
+        <v>331.1039046986455</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19085,28 +19125,28 @@
         <v>0.092</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09111854577203507</v>
+        <v>0.09033516496644614</v>
       </c>
       <c r="J6" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K6" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009530533105775785</v>
+        <v>0.009412357826334539</v>
       </c>
       <c r="M6" t="n">
-        <v>5.803358016727858</v>
+        <v>5.794611746288872</v>
       </c>
       <c r="N6" t="n">
-        <v>48.80601478684013</v>
+        <v>48.7049997477235</v>
       </c>
       <c r="O6" t="n">
-        <v>6.986130172480336</v>
+        <v>6.978896742875875</v>
       </c>
       <c r="P6" t="n">
-        <v>327.999541762699</v>
+        <v>328.0075459916461</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19163,28 +19203,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03610640449639037</v>
+        <v>-0.03541825961226424</v>
       </c>
       <c r="J7" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K7" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01693815272135857</v>
+        <v>0.016365659417657</v>
       </c>
       <c r="M7" t="n">
-        <v>1.598091470067461</v>
+        <v>1.59797867338051</v>
       </c>
       <c r="N7" t="n">
-        <v>4.279757611667846</v>
+        <v>4.275825690480257</v>
       </c>
       <c r="O7" t="n">
-        <v>2.068757504316987</v>
+        <v>2.067806976117514</v>
       </c>
       <c r="P7" t="n">
-        <v>431.995979348963</v>
+        <v>431.9889481973671</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19222,7 +19262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H451"/>
+  <dimension ref="A1:H452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38163,6 +38203,48 @@
         </is>
       </c>
     </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>-41.38653714945232,174.05982841815455</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>-41.3865432157884,174.05888590803886</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>-41.38654388240515,174.05798714092853</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>-41.386655456424066,174.05706256215427</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>-41.386987520566834,174.0561937651682</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>-41.38808406980342,174.05668220961272</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0352/nzd0352.xlsx
+++ b/data/nzd0352/nzd0352.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H452"/>
+  <dimension ref="A1:H454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>322.28</v>
+        <v>320.88</v>
       </c>
       <c r="C452" t="n">
         <v>343.83</v>
@@ -13996,6 +13996,66 @@
         <v>432.63</v>
       </c>
       <c r="H452" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:20+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>323.37</v>
+      </c>
+      <c r="C453" t="n">
+        <v>345.3</v>
+      </c>
+      <c r="D453" t="n">
+        <v>342.32</v>
+      </c>
+      <c r="E453" t="n">
+        <v>332.56</v>
+      </c>
+      <c r="F453" t="n">
+        <v>329.17</v>
+      </c>
+      <c r="G453" t="n">
+        <v>432.64</v>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>323.35</v>
+      </c>
+      <c r="C454" t="n">
+        <v>344.41</v>
+      </c>
+      <c r="D454" t="n">
+        <v>342.02</v>
+      </c>
+      <c r="E454" t="n">
+        <v>331.55</v>
+      </c>
+      <c r="F454" t="n">
+        <v>329.61</v>
+      </c>
+      <c r="G454" t="n">
+        <v>432.66</v>
+      </c>
+      <c r="H454" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14012,7 +14072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B463"/>
+  <dimension ref="A1:B465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18645,6 +18705,26 @@
       </c>
       <c r="B463" t="n">
         <v>0.25</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>
@@ -18813,28 +18893,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.217391445854439</v>
+        <v>1.23893915457491</v>
       </c>
       <c r="J2" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K2" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04033958614015942</v>
+        <v>0.04205232143831816</v>
       </c>
       <c r="M2" t="n">
-        <v>38.03349923729091</v>
+        <v>37.96582928057927</v>
       </c>
       <c r="N2" t="n">
-        <v>1985.430085278093</v>
+        <v>1979.362566140131</v>
       </c>
       <c r="O2" t="n">
-        <v>44.55816519200598</v>
+        <v>44.49002771565927</v>
       </c>
       <c r="P2" t="n">
-        <v>265.5053538554376</v>
+        <v>265.283351138202</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18891,28 +18971,28 @@
         <v>0.1532</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09398327661741454</v>
+        <v>0.0955771707024318</v>
       </c>
       <c r="J3" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K3" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003170817154295791</v>
+        <v>0.003310184260933546</v>
       </c>
       <c r="M3" t="n">
-        <v>7.652097695271117</v>
+        <v>7.623908544893994</v>
       </c>
       <c r="N3" t="n">
-        <v>157.4766233134382</v>
+        <v>156.7972510869116</v>
       </c>
       <c r="O3" t="n">
-        <v>12.54896901396438</v>
+        <v>12.52187091000828</v>
       </c>
       <c r="P3" t="n">
-        <v>340.5114019191872</v>
+        <v>340.4950720451822</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18969,28 +19049,28 @@
         <v>0.0784</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03432589734878678</v>
+        <v>-0.03470381257315546</v>
       </c>
       <c r="J4" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K4" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003286716760777963</v>
+        <v>0.003391450854554168</v>
       </c>
       <c r="M4" t="n">
-        <v>3.633104031292895</v>
+        <v>3.618983053569629</v>
       </c>
       <c r="N4" t="n">
-        <v>20.26362549520682</v>
+        <v>20.17510070765818</v>
       </c>
       <c r="O4" t="n">
-        <v>4.501513689327938</v>
+        <v>4.491670146800429</v>
       </c>
       <c r="P4" t="n">
-        <v>343.5144926539115</v>
+        <v>343.5183667280813</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19047,28 +19127,28 @@
         <v>0.0551</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2734985962606997</v>
+        <v>0.2680919509528285</v>
       </c>
       <c r="J5" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K5" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08478662609242138</v>
+        <v>0.08217701405893663</v>
       </c>
       <c r="M5" t="n">
-        <v>5.580936785198328</v>
+        <v>5.585264238520285</v>
       </c>
       <c r="N5" t="n">
-        <v>45.78999459588035</v>
+        <v>45.7613023750329</v>
       </c>
       <c r="O5" t="n">
-        <v>6.76683046897736</v>
+        <v>6.764710073242822</v>
       </c>
       <c r="P5" t="n">
-        <v>331.1039046986455</v>
+        <v>331.1593150130367</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19125,28 +19205,28 @@
         <v>0.092</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09033516496644614</v>
+        <v>0.08947084520871536</v>
       </c>
       <c r="J6" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K6" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009412357826334539</v>
+        <v>0.009322329677504682</v>
       </c>
       <c r="M6" t="n">
-        <v>5.794611746288872</v>
+        <v>5.77353029557749</v>
       </c>
       <c r="N6" t="n">
-        <v>48.7049997477235</v>
+        <v>48.49458527287798</v>
       </c>
       <c r="O6" t="n">
-        <v>6.978896742875875</v>
+        <v>6.963805372989539</v>
       </c>
       <c r="P6" t="n">
-        <v>328.0075459916461</v>
+        <v>328.016401407147</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19203,28 +19283,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03541825961226424</v>
+        <v>-0.03404477237127266</v>
       </c>
       <c r="J7" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K7" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L7" t="n">
-        <v>0.016365659417657</v>
+        <v>0.01524472858810444</v>
       </c>
       <c r="M7" t="n">
-        <v>1.59797867338051</v>
+        <v>1.597707528666841</v>
       </c>
       <c r="N7" t="n">
-        <v>4.275825690480257</v>
+        <v>4.268072025964093</v>
       </c>
       <c r="O7" t="n">
-        <v>2.067806976117514</v>
+        <v>2.065931273291562</v>
       </c>
       <c r="P7" t="n">
-        <v>431.9889481973671</v>
+        <v>431.9748729373621</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19262,7 +19342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H452"/>
+  <dimension ref="A1:H454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38211,7 +38291,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>-41.38653714945232,174.05982841815455</t>
+          <t>-41.38652497034448,174.05983275507154</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -38240,6 +38320,90 @@
         </is>
       </c>
       <c r="H452" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:20+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>-41.38654663175758,174.05982504155384</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>-41.38655636214625,174.0588838214783</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>-41.386541927916085,174.0579867080742</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>-41.38665727207175,174.05706361584882</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>-41.38699129938692,174.05619837964824</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>-41.388084120728415,174.05668230825742</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>-41.38654645777032,174.0598251035098</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>-41.38654840278673,174.05888508477017</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>-41.38653926270369,174.0579861178183</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>-41.38664893659823,174.0570587784334</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>-41.3869942163707,174.05620194170342</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>-41.388084222578364,174.05668250554686</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0352/nzd0352.xlsx
+++ b/data/nzd0352/nzd0352.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H454"/>
+  <dimension ref="A1:H456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14056,6 +14056,66 @@
         <v>432.66</v>
       </c>
       <c r="H454" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>306.1</v>
+      </c>
+      <c r="C455" t="n">
+        <v>341.9</v>
+      </c>
+      <c r="D455" t="n">
+        <v>341.86</v>
+      </c>
+      <c r="E455" t="n">
+        <v>331.57</v>
+      </c>
+      <c r="F455" t="n">
+        <v>328.33</v>
+      </c>
+      <c r="G455" t="n">
+        <v>432.75</v>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>297.07</v>
+      </c>
+      <c r="C456" t="n">
+        <v>337.22</v>
+      </c>
+      <c r="D456" t="n">
+        <v>341.24</v>
+      </c>
+      <c r="E456" t="n">
+        <v>330.51</v>
+      </c>
+      <c r="F456" t="n">
+        <v>327.38</v>
+      </c>
+      <c r="G456" t="n">
+        <v>432.04</v>
+      </c>
+      <c r="H456" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14072,7 +14132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B465"/>
+  <dimension ref="A1:B467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18725,6 +18785,26 @@
       </c>
       <c r="B465" t="n">
         <v>0.64</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>
@@ -18893,28 +18973,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.23893915457491</v>
+        <v>1.241836251773113</v>
       </c>
       <c r="J2" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="K2" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04205232143831816</v>
+        <v>0.04262990289889934</v>
       </c>
       <c r="M2" t="n">
-        <v>37.96582928057927</v>
+        <v>37.81729251068798</v>
       </c>
       <c r="N2" t="n">
-        <v>1979.362566140131</v>
+        <v>1970.78257605979</v>
       </c>
       <c r="O2" t="n">
-        <v>44.49002771565927</v>
+        <v>44.39349700192349</v>
       </c>
       <c r="P2" t="n">
-        <v>265.283351138202</v>
+        <v>265.2533939055114</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18971,28 +19051,28 @@
         <v>0.1532</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0955771707024318</v>
+        <v>0.09260425099263447</v>
       </c>
       <c r="J3" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="K3" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003310184260933546</v>
+        <v>0.003136492401219049</v>
       </c>
       <c r="M3" t="n">
-        <v>7.623908544893994</v>
+        <v>7.610240068104545</v>
       </c>
       <c r="N3" t="n">
-        <v>156.7972510869116</v>
+        <v>156.1844205098315</v>
       </c>
       <c r="O3" t="n">
-        <v>12.52187091000828</v>
+        <v>12.49737654509263</v>
       </c>
       <c r="P3" t="n">
-        <v>340.4950720451822</v>
+        <v>340.5256823357805</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19049,28 +19129,28 @@
         <v>0.0784</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03470381257315546</v>
+        <v>-0.0355978711207957</v>
       </c>
       <c r="J4" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="K4" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003391450854554168</v>
+        <v>0.003601237011853442</v>
       </c>
       <c r="M4" t="n">
-        <v>3.618983053569629</v>
+        <v>3.607555064985844</v>
       </c>
       <c r="N4" t="n">
-        <v>20.17510070765818</v>
+        <v>20.09157269233605</v>
       </c>
       <c r="O4" t="n">
-        <v>4.491670146800429</v>
+        <v>4.482362400825713</v>
       </c>
       <c r="P4" t="n">
-        <v>343.5183667280813</v>
+        <v>343.5275705782568</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19127,28 +19207,28 @@
         <v>0.0551</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2680919509528285</v>
+        <v>0.2619025043277657</v>
       </c>
       <c r="J5" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="K5" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08217701405893663</v>
+        <v>0.07905677171947056</v>
       </c>
       <c r="M5" t="n">
-        <v>5.585264238520285</v>
+        <v>5.594102061041921</v>
       </c>
       <c r="N5" t="n">
-        <v>45.7613023750329</v>
+        <v>45.7886132554576</v>
       </c>
       <c r="O5" t="n">
-        <v>6.764710073242822</v>
+        <v>6.766728401188982</v>
       </c>
       <c r="P5" t="n">
-        <v>331.1593150130367</v>
+        <v>331.2230251399941</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19205,28 +19285,28 @@
         <v>0.092</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08947084520871536</v>
+        <v>0.08729642350305972</v>
       </c>
       <c r="J6" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="K6" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009322329677504682</v>
+        <v>0.008958351572853296</v>
       </c>
       <c r="M6" t="n">
-        <v>5.77353029557749</v>
+        <v>5.759317795474871</v>
       </c>
       <c r="N6" t="n">
-        <v>48.49458527287798</v>
+        <v>48.31045318966625</v>
       </c>
       <c r="O6" t="n">
-        <v>6.963805372989539</v>
+        <v>6.950572148367805</v>
       </c>
       <c r="P6" t="n">
-        <v>328.016401407147</v>
+        <v>328.038784732273</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19283,28 +19363,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03404477237127266</v>
+        <v>-0.0329148096190379</v>
       </c>
       <c r="J7" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="K7" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01524472858810444</v>
+        <v>0.01437244440954299</v>
       </c>
       <c r="M7" t="n">
-        <v>1.597707528666841</v>
+        <v>1.596194476909629</v>
       </c>
       <c r="N7" t="n">
-        <v>4.268072025964093</v>
+        <v>4.257447483982146</v>
       </c>
       <c r="O7" t="n">
-        <v>2.065931273291562</v>
+        <v>2.063358302375558</v>
       </c>
       <c r="P7" t="n">
-        <v>431.9748729373621</v>
+        <v>431.9632437977147</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19342,7 +19422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H454"/>
+  <dimension ref="A1:H456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38409,6 +38489,90 @@
         </is>
       </c>
     </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>-41.38639639375295,174.05987854042755</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>-41.3865259556042,174.05888864753547</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>-41.386537841257095,174.05798580301519</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-41.38664910165709,174.0570588742238</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>-41.38698573059936,174.056191579362</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>-41.38808468090319,174.05668339334935</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>-41.386317838491856,174.05990651339695</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>-41.386484101892904,174.0588952904543</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>-41.38653233315149,174.05798458315323</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>-41.38664035353612,174.05705379733374</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>-41.38697943256532,174.05618388856354</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>-41.388081065229414,174.0566763895745</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0352/nzd0352.xlsx
+++ b/data/nzd0352/nzd0352.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H456"/>
+  <dimension ref="A1:H459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14116,6 +14116,96 @@
         <v>432.04</v>
       </c>
       <c r="H456" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>282.78</v>
+      </c>
+      <c r="C457" t="n">
+        <v>324.5</v>
+      </c>
+      <c r="D457" t="n">
+        <v>340.31</v>
+      </c>
+      <c r="E457" t="n">
+        <v>328.59</v>
+      </c>
+      <c r="F457" t="n">
+        <v>325.8</v>
+      </c>
+      <c r="G457" t="n">
+        <v>432.27</v>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>264.53</v>
+      </c>
+      <c r="C458" t="n">
+        <v>313.28</v>
+      </c>
+      <c r="D458" t="n">
+        <v>339.37</v>
+      </c>
+      <c r="E458" t="n">
+        <v>327.13</v>
+      </c>
+      <c r="F458" t="n">
+        <v>325.48</v>
+      </c>
+      <c r="G458" t="n">
+        <v>432.55</v>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>264.53</v>
+      </c>
+      <c r="C459" t="n">
+        <v>309.66</v>
+      </c>
+      <c r="D459" t="n">
+        <v>338.03</v>
+      </c>
+      <c r="E459" t="n">
+        <v>327.03</v>
+      </c>
+      <c r="F459" t="n">
+        <v>324.02</v>
+      </c>
+      <c r="G459" t="n">
+        <v>432.28</v>
+      </c>
+      <c r="H459" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14132,7 +14222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B467"/>
+  <dimension ref="A1:B470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18805,6 +18895,36 @@
       </c>
       <c r="B467" t="n">
         <v>0.31</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
@@ -18973,28 +19093,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.241836251773113</v>
+        <v>1.206593392613692</v>
       </c>
       <c r="J2" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="K2" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04262990289889934</v>
+        <v>0.04078942406449182</v>
       </c>
       <c r="M2" t="n">
-        <v>37.81729251068798</v>
+        <v>37.76346294537743</v>
       </c>
       <c r="N2" t="n">
-        <v>1970.78257605979</v>
+        <v>1963.274927513184</v>
       </c>
       <c r="O2" t="n">
-        <v>44.39349700192349</v>
+        <v>44.30885834134281</v>
       </c>
       <c r="P2" t="n">
-        <v>265.2533939055114</v>
+        <v>265.6191676658224</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19051,28 +19171,28 @@
         <v>0.1532</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09260425099263447</v>
+        <v>0.05826615593892556</v>
       </c>
       <c r="J3" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="K3" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003136492401219049</v>
+        <v>0.001222540376393577</v>
       </c>
       <c r="M3" t="n">
-        <v>7.610240068104545</v>
+        <v>7.791634907501709</v>
       </c>
       <c r="N3" t="n">
-        <v>156.1844205098315</v>
+        <v>160.1614944124765</v>
       </c>
       <c r="O3" t="n">
-        <v>12.49737654509263</v>
+        <v>12.65549265783345</v>
       </c>
       <c r="P3" t="n">
-        <v>340.5256823357805</v>
+        <v>340.8801915550221</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19129,28 +19249,28 @@
         <v>0.0784</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0355978711207957</v>
+        <v>-0.03982244394020135</v>
       </c>
       <c r="J4" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="K4" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003601237011853442</v>
+        <v>0.004549398884512335</v>
       </c>
       <c r="M4" t="n">
-        <v>3.607555064985844</v>
+        <v>3.604917096517877</v>
       </c>
       <c r="N4" t="n">
-        <v>20.09157269233605</v>
+        <v>20.03740023139975</v>
       </c>
       <c r="O4" t="n">
-        <v>4.482362400825713</v>
+        <v>4.476315474963728</v>
       </c>
       <c r="P4" t="n">
-        <v>343.5275705782568</v>
+        <v>343.57118928456</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19207,28 +19327,28 @@
         <v>0.0551</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2619025043277657</v>
+        <v>0.248495911921223</v>
       </c>
       <c r="J5" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="K5" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07905677171947056</v>
+        <v>0.07163030422382499</v>
       </c>
       <c r="M5" t="n">
-        <v>5.594102061041921</v>
+        <v>5.631866974850115</v>
       </c>
       <c r="N5" t="n">
-        <v>45.7886132554576</v>
+        <v>46.21495284163328</v>
       </c>
       <c r="O5" t="n">
-        <v>6.766728401188982</v>
+        <v>6.798158047709195</v>
       </c>
       <c r="P5" t="n">
-        <v>331.2230251399941</v>
+        <v>331.3614098344507</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19285,28 +19405,28 @@
         <v>0.092</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08729642350305972</v>
+        <v>0.08064691671958368</v>
       </c>
       <c r="J6" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="K6" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008958351572853296</v>
+        <v>0.007735614506746202</v>
       </c>
       <c r="M6" t="n">
-        <v>5.759317795474871</v>
+        <v>5.755311519720038</v>
       </c>
       <c r="N6" t="n">
-        <v>48.31045318966625</v>
+        <v>48.17569386905482</v>
       </c>
       <c r="O6" t="n">
-        <v>6.950572148367805</v>
+        <v>6.940871261524364</v>
       </c>
       <c r="P6" t="n">
-        <v>328.038784732273</v>
+        <v>328.1074295953881</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19363,28 +19483,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0329148096190379</v>
+        <v>-0.03129351737757426</v>
       </c>
       <c r="J7" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="K7" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01437244440954299</v>
+        <v>0.01316085371595899</v>
       </c>
       <c r="M7" t="n">
-        <v>1.596194476909629</v>
+        <v>1.593559864398688</v>
       </c>
       <c r="N7" t="n">
-        <v>4.257447483982146</v>
+        <v>4.240244751034433</v>
       </c>
       <c r="O7" t="n">
-        <v>2.063358302375558</v>
+        <v>2.05918545814466</v>
       </c>
       <c r="P7" t="n">
-        <v>431.9632437977147</v>
+        <v>431.946510025856</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19422,7 +19542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H456"/>
+  <dimension ref="A1:H459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38573,6 +38693,132 @@
         </is>
       </c>
     </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>-41.38619352455925,174.0599507805647</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>-41.38637034564901,174.0589133455268</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>-41.38652407099303,174.05798275336068</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>-41.38662450788241,174.05704460146086</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>-41.38696895793909,174.0561710975546</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>-41.38808223650407,174.0566786584029</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>-41.38603476111369,174.06000731467262</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>-41.38627000405294,174.05892927141454</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>-41.386515719994115,174.05798090389345</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>-41.386612458582675,174.0570376087689</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>-41.386966836495624,174.056168506971</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>-41.388083662403574,174.05668142045494</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:32+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>-41.38603476111369,174.06000731467262</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>-41.3862376300257,174.05893440970368</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>-41.38650381537857,174.05797826741974</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-41.386611633288155,174.0570371298175</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>-41.38695715740901,174.05615668743553</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>-41.38808228742905,174.05667875704762</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0352/nzd0352.xlsx
+++ b/data/nzd0352/nzd0352.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H459"/>
+  <dimension ref="A1:H460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14206,6 +14206,36 @@
         <v>432.28</v>
       </c>
       <c r="H459" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>236.72</v>
+      </c>
+      <c r="C460" t="n">
+        <v>300.45</v>
+      </c>
+      <c r="D460" t="n">
+        <v>335.65</v>
+      </c>
+      <c r="E460" t="n">
+        <v>324.76</v>
+      </c>
+      <c r="F460" t="n">
+        <v>320.51</v>
+      </c>
+      <c r="G460" t="n">
+        <v>430.7</v>
+      </c>
+      <c r="H460" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14222,7 +14252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B470"/>
+  <dimension ref="A1:B471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18925,6 +18955,16 @@
       </c>
       <c r="B470" t="n">
         <v>-0.29</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>-0.26</v>
       </c>
     </row>
   </sheetData>
@@ -19093,28 +19133,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.206593392613692</v>
+        <v>1.180693789008922</v>
       </c>
       <c r="J2" t="n">
+        <v>459</v>
+      </c>
+      <c r="K2" t="n">
         <v>458</v>
       </c>
-      <c r="K2" t="n">
-        <v>457</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.04078942406449182</v>
+        <v>0.03914814397419297</v>
       </c>
       <c r="M2" t="n">
-        <v>37.76346294537743</v>
+        <v>37.82688162869228</v>
       </c>
       <c r="N2" t="n">
-        <v>1963.274927513184</v>
+        <v>1967.093226714284</v>
       </c>
       <c r="O2" t="n">
-        <v>44.30885834134281</v>
+        <v>44.35192472389765</v>
       </c>
       <c r="P2" t="n">
-        <v>265.6191676658224</v>
+        <v>265.8888546644168</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19171,28 +19211,28 @@
         <v>0.1532</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05826615593892556</v>
+        <v>0.040587660313373</v>
       </c>
       <c r="J3" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K3" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001222540376393577</v>
+        <v>0.0005825164362587287</v>
       </c>
       <c r="M3" t="n">
-        <v>7.791634907501709</v>
+        <v>7.89743743188968</v>
       </c>
       <c r="N3" t="n">
-        <v>160.1614944124765</v>
+        <v>163.6268829264671</v>
       </c>
       <c r="O3" t="n">
-        <v>12.65549265783345</v>
+        <v>12.79167240537636</v>
       </c>
       <c r="P3" t="n">
-        <v>340.8801915550221</v>
+        <v>341.063316092873</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19249,28 +19289,28 @@
         <v>0.0784</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03982244394020135</v>
+        <v>-0.04270874267115492</v>
       </c>
       <c r="J4" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K4" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004549398884512335</v>
+        <v>0.005227429182104171</v>
       </c>
       <c r="M4" t="n">
-        <v>3.604917096517877</v>
+        <v>3.611407175262625</v>
       </c>
       <c r="N4" t="n">
-        <v>20.03740023139975</v>
+        <v>20.09541968115577</v>
       </c>
       <c r="O4" t="n">
-        <v>4.476315474963728</v>
+        <v>4.482791505430045</v>
       </c>
       <c r="P4" t="n">
-        <v>343.57118928456</v>
+        <v>343.6010873105233</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19327,28 +19367,28 @@
         <v>0.0551</v>
       </c>
       <c r="I5" t="n">
-        <v>0.248495911921223</v>
+        <v>0.2429201866225966</v>
       </c>
       <c r="J5" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K5" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07163030422382499</v>
+        <v>0.06844907974928471</v>
       </c>
       <c r="M5" t="n">
-        <v>5.631866974850115</v>
+        <v>5.651182329783865</v>
       </c>
       <c r="N5" t="n">
-        <v>46.21495284163328</v>
+        <v>46.4936949823116</v>
       </c>
       <c r="O5" t="n">
-        <v>6.798158047709195</v>
+        <v>6.81862852649355</v>
       </c>
       <c r="P5" t="n">
-        <v>331.3614098344507</v>
+        <v>331.4191665655731</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19405,28 +19445,28 @@
         <v>0.092</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08064691671958368</v>
+        <v>0.07654238490004159</v>
       </c>
       <c r="J6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007735614506746202</v>
+        <v>0.006976808492220599</v>
       </c>
       <c r="M6" t="n">
-        <v>5.755311519720038</v>
+        <v>5.763507898397606</v>
       </c>
       <c r="N6" t="n">
-        <v>48.17569386905482</v>
+        <v>48.27635067261274</v>
       </c>
       <c r="O6" t="n">
-        <v>6.940871261524364</v>
+        <v>6.948118498745739</v>
       </c>
       <c r="P6" t="n">
-        <v>328.1074295953881</v>
+        <v>328.1499468156578</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19483,28 +19523,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03129351737757426</v>
+        <v>-0.03146458926432984</v>
       </c>
       <c r="J7" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K7" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01316085371595899</v>
+        <v>0.01336436767629923</v>
       </c>
       <c r="M7" t="n">
-        <v>1.593559864398688</v>
+        <v>1.591022715090007</v>
       </c>
       <c r="N7" t="n">
-        <v>4.240244751034433</v>
+        <v>4.231363922699986</v>
       </c>
       <c r="O7" t="n">
-        <v>2.05918545814466</v>
+        <v>2.057027934350913</v>
       </c>
       <c r="P7" t="n">
-        <v>431.946510025856</v>
+        <v>431.9482820918092</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19542,7 +19582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H459"/>
+  <dimension ref="A1:H460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38819,6 +38859,48 @@
         </is>
       </c>
     </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>-41.38579283166532,174.06009346284532</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>-41.38615526405975,174.05894748251168</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>-41.38648267135966,174.0579735847301</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-41.386592899101935,174.05702625762382</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>-41.38693388781886,174.0561282719913</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>-41.388074241280535,174.05666317118465</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
